--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\world\api\model\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA48A41-CCA9-4F74-8119-4416825C3E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DA1C37-8F12-41E7-8CB3-62BDB5BCE7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1470" windowWidth="19125" windowHeight="9930" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
     <sheet name="t_wenyan" sheetId="2" r:id="rId2"/>
+    <sheet name="t_microservice" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="309">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -879,6 +880,158 @@
   </si>
   <si>
     <t>具体事物，不占用空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BROKER001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国泰君安期货公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工商银行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BROKER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRADER001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XCHG001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XCHG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期货投资者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CP001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中心期货公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BROKER002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国泰君安期货服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中信期货服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海期货交易所服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海期货交易所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国证券登记结算有限责任公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国结算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.chinaclear.cn/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABBRE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRADER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GTJA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZXQH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHFE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSDC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICBC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郑州商品交易所服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大连商品交易所服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郑州商品交易所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大连商品交易所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZCE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOGO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5988,4 +6141,261 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EFBA747-D049-4A0C-AB02-72161AC7BBC3}">
+  <dimension ref="B2:I10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" customWidth="1"/>
+    <col min="5" max="5" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.375" customWidth="1"/>
+    <col min="9" max="9" width="29.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2" t="s">
+        <v>308</v>
+      </c>
+      <c r="H2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F5" t="s">
+        <v>276</v>
+      </c>
+      <c r="G5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H5" t="s">
+        <v>254</v>
+      </c>
+      <c r="I5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H6" t="s">
+        <v>254</v>
+      </c>
+      <c r="I6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" t="s">
+        <v>302</v>
+      </c>
+      <c r="F7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7" t="s">
+        <v>254</v>
+      </c>
+      <c r="H7" t="s">
+        <v>254</v>
+      </c>
+      <c r="I7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" t="s">
+        <v>306</v>
+      </c>
+      <c r="E8" t="s">
+        <v>303</v>
+      </c>
+      <c r="F8" t="s">
+        <v>281</v>
+      </c>
+      <c r="G8" t="s">
+        <v>254</v>
+      </c>
+      <c r="H8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F9" t="s">
+        <v>283</v>
+      </c>
+      <c r="G9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I9" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" t="s">
+        <v>301</v>
+      </c>
+      <c r="E10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F10" t="s">
+        <v>277</v>
+      </c>
+      <c r="G10" t="s">
+        <v>254</v>
+      </c>
+      <c r="H10" t="s">
+        <v>254</v>
+      </c>
+      <c r="I10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H9" r:id="rId1" xr:uid="{03F3A1EF-4E61-437E-8063-A663D4F5E404}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
 </file>
--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,14 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DA1C37-8F12-41E7-8CB3-62BDB5BCE7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F5760F-F23A-43A2-A9D1-A224C46CF3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1470" windowWidth="19125" windowHeight="9930" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
     <sheet name="t_wenyan" sheetId="2" r:id="rId2"/>
     <sheet name="t_microservice" sheetId="3" r:id="rId3"/>
+    <sheet name="t_trader" sheetId="4" r:id="rId4"/>
+    <sheet name="t_broker" sheetId="5" r:id="rId5"/>
+    <sheet name="t_bank" sheetId="6" r:id="rId6"/>
+    <sheet name="t_exchange" sheetId="7" r:id="rId7"/>
+    <sheet name="T_clearinghouse" sheetId="8" r:id="rId8"/>
+    <sheet name="t_security" sheetId="10" r:id="rId9"/>
+    <sheet name="t_trader_security" sheetId="11" r:id="rId10"/>
+    <sheet name="t_settlement" sheetId="13" r:id="rId11"/>
+    <sheet name="t_transfer_journal" sheetId="14" r:id="rId12"/>
+    <sheet name="t_bank_account" sheetId="19" r:id="rId13"/>
+    <sheet name="t_future_account" sheetId="16" r:id="rId14"/>
+    <sheet name="t_stock_account" sheetId="17" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="378">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1032,6 +1044,282 @@
   </si>
   <si>
     <t>LOGO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐清华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210222198205135019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FUND_CARD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_CARD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62201234567909</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XQH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通交易者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE_TIME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPDATE_TIME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/14/2025 1:59 PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XZL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CQL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐忠良</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曹庆菊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRADER002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRADER003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国泰君安</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中信期货</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通券商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招商银行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CMBC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通银行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上期所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郑商所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大商所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通交易所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RB2510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>螺纹钢2510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MA2509</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲醇2509</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SECURITY_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T_TRADER_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quantity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐清华持有螺纹钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐清华持有甲醇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPEN_DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLOSE_DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/14/2024 1:59 PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11/1/2024 1:59 PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/1/2024 1:59 PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FUTURE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STOCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大秦铁路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海建工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期货</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVESTOR_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BALANCE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK_ACCOUNT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MARGIN_ACCOUNT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62201234567908</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62201234567906</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62201234567907</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票资金账户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期货资金账户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行账户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMOUNT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STATUS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREDIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>83376426</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>83376428</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1683259</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1683258</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62257101010044792</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62257101010044791</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SETTLE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1039,6 +1327,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1084,9 +1375,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5991,6 +6287,581 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DC1D71-1648-4D08-A33F-750C29F62A91}">
+  <dimension ref="B2:G6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>45791.59375</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>45791.59375</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3">
+        <v>45791.59375</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3">
+        <v>45791.59375</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED01824-373C-4B7A-A388-A735C9E31FD9}">
+  <dimension ref="B2:G6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E3" s="6">
+        <v>3023.0010000000002</v>
+      </c>
+      <c r="F3" s="5">
+        <v>45791</v>
+      </c>
+      <c r="G3" s="3">
+        <v>45791.600694444445</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E4" s="6">
+        <v>3230.0010000000002</v>
+      </c>
+      <c r="F4" s="5">
+        <v>45791</v>
+      </c>
+      <c r="G4" s="3">
+        <v>45792</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5">
+        <v>601006</v>
+      </c>
+      <c r="E5" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="F5" s="5">
+        <v>45791</v>
+      </c>
+      <c r="G5" s="3">
+        <v>45793</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6">
+        <v>601170</v>
+      </c>
+      <c r="E6" s="6">
+        <v>3.42</v>
+      </c>
+      <c r="F6" s="5">
+        <v>45791</v>
+      </c>
+      <c r="G6" s="3">
+        <v>45794</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F304A949-FFD7-49F1-B58D-74D342C4AF6C}">
+  <dimension ref="B2:H4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F2" t="s">
+        <v>367</v>
+      </c>
+      <c r="G2" t="s">
+        <v>368</v>
+      </c>
+      <c r="H2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>45791.611805555556</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>45791.611805555556</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9305FC59-37FF-415A-A3B7-01239A431D79}">
+  <dimension ref="B3:H5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E4" s="4">
+        <v>3023</v>
+      </c>
+      <c r="F4" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="G4" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="H4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E5" s="4">
+        <v>3230</v>
+      </c>
+      <c r="F5" s="3">
+        <v>45792</v>
+      </c>
+      <c r="G5" s="3">
+        <v>45792</v>
+      </c>
+      <c r="H5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEE4E1E-4960-4128-9003-4ABF67067429}">
+  <dimension ref="B2:H4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3023</v>
+      </c>
+      <c r="F3" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="G3" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="H3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E4" s="4">
+        <v>3230</v>
+      </c>
+      <c r="F4" s="3">
+        <v>45792</v>
+      </c>
+      <c r="G4" s="3">
+        <v>45792</v>
+      </c>
+      <c r="H4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883BD7DA-ECA5-459C-A285-7074F9420849}">
+  <dimension ref="B3:G5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E4" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="F4" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="G4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E5" s="3">
+        <v>45792</v>
+      </c>
+      <c r="F5" s="3">
+        <v>45792</v>
+      </c>
+      <c r="G5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBFA0B0-09A3-4E87-9D3C-50BFACFA9A69}">
   <dimension ref="B2:F9"/>
@@ -6398,4 +7269,701 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6ABADF-5314-402D-971B-634CB3A368D4}">
+  <dimension ref="B2:K5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>359</v>
+      </c>
+      <c r="I2" t="s">
+        <v>316</v>
+      </c>
+      <c r="J2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>324</v>
+      </c>
+      <c r="D5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{393D472E-32AC-4542-A27D-D437AC0EBDB2}">
+  <dimension ref="B2:J4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EDEDC8F-B01A-419B-863E-70DB54F0A6BC}">
+  <dimension ref="B2:H4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E1187D-5C4A-430F-BF47-6AFC622CE742}">
+  <dimension ref="B2:H5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E5" t="s">
+        <v>333</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0675BA7A-8C70-4B4E-9B58-D659F9873D63}">
+  <dimension ref="B2:H3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A4C484-61ED-4789-AC9F-B41CA87A679E}">
+  <dimension ref="B2:K6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G2" t="s">
+        <v>344</v>
+      </c>
+      <c r="H2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I2" t="s">
+        <v>316</v>
+      </c>
+      <c r="J2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E4" t="s">
+        <v>335</v>
+      </c>
+      <c r="F4" t="s">
+        <v>338</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5">
+        <v>601006</v>
+      </c>
+      <c r="E5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6">
+        <v>601170</v>
+      </c>
+      <c r="E6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F5760F-F23A-43A2-A9D1-A224C46CF3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408A5AA9-7963-4503-9263-A9841AC53274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="382">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1251,10 +1251,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>62201234567908</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1320,6 +1316,24 @@
   </si>
   <si>
     <t>SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>----------------</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MACCT1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MACCT2</t>
+  </si>
+  <si>
+    <t>MACCT3</t>
+  </si>
+  <si>
+    <t>--------------------------------</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1375,7 +1389,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1383,6 +1397,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6425,7 +6440,7 @@
         <v>272</v>
       </c>
       <c r="E2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F2" t="s">
         <v>355</v>
@@ -6543,16 +6558,16 @@
         <v>257</v>
       </c>
       <c r="D2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G2" t="s">
         <v>367</v>
-      </c>
-      <c r="G2" t="s">
-        <v>368</v>
       </c>
       <c r="H2" t="s">
         <v>316</v>
@@ -6654,7 +6669,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E4" s="4">
         <v>3023</v>
@@ -6666,7 +6681,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="H4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
@@ -6677,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E5" s="4">
         <v>3230</v>
@@ -6689,7 +6704,7 @@
         <v>45792</v>
       </c>
       <c r="H5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -6740,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E3" s="4">
         <v>3023</v>
@@ -6752,7 +6767,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="H3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
@@ -6763,7 +6778,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E4" s="4">
         <v>3230</v>
@@ -6775,7 +6790,7 @@
         <v>45792</v>
       </c>
       <c r="H4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -6824,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E4" s="3">
         <v>45791.600694444445</v>
@@ -6833,7 +6848,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="G4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -6844,7 +6859,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E5" s="3">
         <v>45792</v>
@@ -6853,7 +6868,7 @@
         <v>45792</v>
       </c>
       <c r="G5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -7273,16 +7288,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6ABADF-5314-402D-971B-634CB3A368D4}">
-  <dimension ref="B2:K5"/>
+  <dimension ref="B2:K6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="20.5" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
@@ -7319,34 +7332,34 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D3" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K3" t="s">
-        <v>315</v>
+        <v>0</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
@@ -7354,22 +7367,22 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>323</v>
+        <v>279</v>
       </c>
       <c r="D4" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E4" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>310</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>318</v>
@@ -7386,22 +7399,22 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>310</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>318</v>
@@ -7410,12 +7423,45 @@
         <v>318</v>
       </c>
       <c r="K5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" t="s">
+        <v>320</v>
+      </c>
+      <c r="E6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K6" t="s">
         <v>315</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408A5AA9-7963-4503-9263-A9841AC53274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30267141-757B-48AE-800B-B64ED061B3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="386">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1251,18 +1251,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>62201234567908</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>62201234567906</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>62201234567907</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>股票资金账户</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1323,17 +1311,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MACCT1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MACCT2</t>
-  </si>
-  <si>
-    <t>MACCT3</t>
-  </si>
-  <si>
     <t>--------------------------------</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-15T15:02:12.776936800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MACCT001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MACCT002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MACCT003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>134173757291036808</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>484042476845528095</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>848318999589192967</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3677025957558384313</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0395326568385866590</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5215585883581452342</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6440,7 +6458,7 @@
         <v>272</v>
       </c>
       <c r="E2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F2" t="s">
         <v>355</v>
@@ -6558,16 +6576,16 @@
         <v>257</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H2" t="s">
         <v>316</v>
@@ -6669,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E4" s="4">
         <v>3023</v>
@@ -6681,7 +6699,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="H4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
@@ -6692,7 +6710,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E5" s="4">
         <v>3230</v>
@@ -6704,7 +6722,7 @@
         <v>45792</v>
       </c>
       <c r="H5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -6755,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E3" s="4">
         <v>3023</v>
@@ -6767,7 +6785,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="H3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
@@ -6778,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E4" s="4">
         <v>3230</v>
@@ -6790,7 +6808,7 @@
         <v>45792</v>
       </c>
       <c r="H4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -6839,7 +6857,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E4" s="3">
         <v>45791.600694444445</v>
@@ -6848,7 +6866,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="G4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -6859,7 +6877,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E5" s="3">
         <v>45792</v>
@@ -6868,7 +6886,7 @@
         <v>45792</v>
       </c>
       <c r="G5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -7293,9 +7311,7 @@
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="36.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="36.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
@@ -7335,31 +7351,31 @@
         <v>0</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
@@ -7376,19 +7392,19 @@
         <v>309</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="K4" t="s">
         <v>315</v>
@@ -7396,7 +7412,7 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
         <v>323</v>
@@ -7408,19 +7424,19 @@
         <v>321</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>310</v>
+        <v>381</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="K5" t="s">
         <v>315</v>
@@ -7428,7 +7444,7 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>324</v>
@@ -7440,19 +7456,19 @@
         <v>322</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>310</v>
+        <v>382</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="K6" t="s">
         <v>315</v>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30267141-757B-48AE-800B-B64ED061B3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14861BB1-B43E-41DB-9FF1-30C0E9EA6339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="387">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1195,18 +1195,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5/14/2024 1:59 PM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11/1/2024 1:59 PM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10/1/2024 1:59 PM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FUTURE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1352,6 +1340,22 @@
   </si>
   <si>
     <t>5215585883581452342</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>------------------------------------------------</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-----------------</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-----------------------</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>------------------------</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1359,8 +1363,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-m\-d\ h:mm:ss"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1407,7 +1412,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1416,6 +1421,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6458,10 +6464,10 @@
         <v>272</v>
       </c>
       <c r="E2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G2" t="s">
         <v>316</v>
@@ -6472,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D3" t="s">
         <v>335</v>
@@ -6492,7 +6498,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D4" t="s">
         <v>337</v>
@@ -6512,7 +6518,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D5">
         <v>601006</v>
@@ -6532,7 +6538,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D6">
         <v>601170</v>
@@ -6576,16 +6582,16 @@
         <v>257</v>
       </c>
       <c r="D2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H2" t="s">
         <v>316</v>
@@ -6596,7 +6602,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6619,7 +6625,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6661,13 +6667,13 @@
         <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D3" t="s">
         <v>272</v>
       </c>
       <c r="E3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F3" t="s">
         <v>316</v>
@@ -6687,7 +6693,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E4" s="4">
         <v>3023</v>
@@ -6699,7 +6705,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="H4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
@@ -6710,7 +6716,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E5" s="4">
         <v>3230</v>
@@ -6722,7 +6728,7 @@
         <v>45792</v>
       </c>
       <c r="H5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -6747,13 +6753,13 @@
         <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
         <v>272</v>
       </c>
       <c r="E2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F2" t="s">
         <v>316</v>
@@ -6773,7 +6779,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E3" s="4">
         <v>3023</v>
@@ -6785,7 +6791,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="H3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
@@ -6796,7 +6802,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E4" s="4">
         <v>3230</v>
@@ -6808,7 +6814,7 @@
         <v>45792</v>
       </c>
       <c r="H4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -6834,7 +6840,7 @@
         <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D3" t="s">
         <v>272</v>
@@ -6857,7 +6863,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E4" s="3">
         <v>45791.600694444445</v>
@@ -6866,7 +6872,7 @@
         <v>45791.600694444445</v>
       </c>
       <c r="G4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -6877,7 +6883,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E5" s="3">
         <v>45792</v>
@@ -6886,7 +6892,7 @@
         <v>45792</v>
       </c>
       <c r="G5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -7331,10 +7337,10 @@
         <v>312</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I2" t="s">
         <v>316</v>
@@ -7351,31 +7357,31 @@
         <v>0</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
@@ -7392,19 +7398,19 @@
         <v>309</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K4" t="s">
         <v>315</v>
@@ -7424,19 +7430,19 @@
         <v>321</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K5" t="s">
         <v>315</v>
@@ -7456,19 +7462,19 @@
         <v>322</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>385</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K6" t="s">
         <v>315</v>
@@ -7856,16 +7862,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A4C484-61ED-4789-AC9F-B41CA87A679E}">
-  <dimension ref="B2:K6"/>
+  <dimension ref="B2:K7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="53.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
@@ -7902,66 +7907,66 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K3" t="s">
-        <v>353</v>
+        <v>0</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G3" s="8">
+        <v>45792.931250000001</v>
+      </c>
+      <c r="H3" s="8">
+        <v>45792.931250000001</v>
+      </c>
+      <c r="I3" s="8">
+        <v>45792.931250000001</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E4" t="s">
         <v>335</v>
       </c>
       <c r="F4" t="s">
-        <v>338</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>318</v>
+        <v>336</v>
+      </c>
+      <c r="G4" s="8">
+        <v>45792.931250000001</v>
+      </c>
+      <c r="H4" s="8">
+        <v>45792.931250000001</v>
+      </c>
+      <c r="I4" s="8">
+        <v>45792.931250000001</v>
+      </c>
+      <c r="J4" s="8">
+        <v>45792.931250000001</v>
       </c>
       <c r="K4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
@@ -7969,59 +7974,95 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D5" t="s">
+        <v>337</v>
+      </c>
+      <c r="E5" t="s">
+        <v>335</v>
+      </c>
+      <c r="F5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G5" s="8">
+        <v>45793.931250000001</v>
+      </c>
+      <c r="H5" s="8">
+        <v>45793.931250000001</v>
+      </c>
+      <c r="I5" s="8">
+        <v>45793.931250000001</v>
+      </c>
+      <c r="J5" s="8">
+        <v>45793.931250000001</v>
+      </c>
+      <c r="K5" t="s">
         <v>350</v>
-      </c>
-      <c r="D5">
-        <v>601006</v>
-      </c>
-      <c r="E5" t="s">
-        <v>351</v>
-      </c>
-      <c r="F5" t="s">
-        <v>351</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K5" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6">
+        <v>601006</v>
+      </c>
+      <c r="E6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F6" t="s">
+        <v>348</v>
+      </c>
+      <c r="G6" s="8">
+        <v>45794.931250000001</v>
+      </c>
+      <c r="H6" s="8">
+        <v>45794.931250000001</v>
+      </c>
+      <c r="I6" s="8">
+        <v>45794.931250000001</v>
+      </c>
+      <c r="J6" s="8">
+        <v>45794.931250000001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>350</v>
-      </c>
-      <c r="D6">
+      <c r="C7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D7">
         <v>601170</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
+        <v>348</v>
+      </c>
+      <c r="F7" t="s">
+        <v>349</v>
+      </c>
+      <c r="G7" s="8">
+        <v>45795.931250000001</v>
+      </c>
+      <c r="H7" s="8">
+        <v>45795.931250000001</v>
+      </c>
+      <c r="I7" s="8">
+        <v>45795.931250000001</v>
+      </c>
+      <c r="J7" s="8">
+        <v>45795.931250000001</v>
+      </c>
+      <c r="K7" t="s">
         <v>351</v>
-      </c>
-      <c r="F6" t="s">
-        <v>352</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K6" t="s">
-        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14861BB1-B43E-41DB-9FF1-30C0E9EA6339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F1CC14-14A1-46F1-98F3-17FB8FA9C4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="389">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1356,6 +1356,14 @@
   </si>
   <si>
     <t>------------------------</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CZCE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHEX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7862,18 +7870,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A4C484-61ED-4789-AC9F-B41CA87A679E}">
-  <dimension ref="B2:K7"/>
+  <dimension ref="B2:L7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="53.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="53.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>239</v>
       </c>
@@ -7881,31 +7891,34 @@
         <v>257</v>
       </c>
       <c r="D2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E2" t="s">
         <v>272</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>295</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>271</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>344</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>345</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>316</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>317</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>0</v>
       </c>
@@ -7916,13 +7929,13 @@
         <v>384</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>386</v>
-      </c>
-      <c r="G3" s="8">
-        <v>45792.931250000001</v>
       </c>
       <c r="H3" s="8">
         <v>45792.931250000001</v>
@@ -7930,14 +7943,17 @@
       <c r="I3" s="8">
         <v>45792.931250000001</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>383</v>
+      <c r="J3" s="8">
+        <v>45792.931250000001</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L3" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>1</v>
       </c>
@@ -7945,16 +7961,16 @@
         <v>346</v>
       </c>
       <c r="D4" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="E4" t="s">
         <v>335</v>
       </c>
       <c r="F4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G4" t="s">
         <v>336</v>
-      </c>
-      <c r="G4" s="8">
-        <v>45792.931250000001</v>
       </c>
       <c r="H4" s="8">
         <v>45792.931250000001</v>
@@ -7965,11 +7981,14 @@
       <c r="J4" s="8">
         <v>45792.931250000001</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="8">
+        <v>45792.931250000001</v>
+      </c>
+      <c r="L4" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2</v>
       </c>
@@ -7977,16 +7996,16 @@
         <v>346</v>
       </c>
       <c r="D5" t="s">
+        <v>387</v>
+      </c>
+      <c r="E5" t="s">
         <v>337</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>335</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>338</v>
-      </c>
-      <c r="G5" s="8">
-        <v>45793.931250000001</v>
       </c>
       <c r="H5" s="8">
         <v>45793.931250000001</v>
@@ -7997,28 +8016,31 @@
       <c r="J5" s="8">
         <v>45793.931250000001</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="8">
+        <v>45793.931250000001</v>
+      </c>
+      <c r="L5" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>347</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E6">
         <v>601006</v>
-      </c>
-      <c r="E6" t="s">
-        <v>348</v>
       </c>
       <c r="F6" t="s">
         <v>348</v>
       </c>
-      <c r="G6" s="8">
-        <v>45794.931250000001</v>
+      <c r="G6" t="s">
+        <v>348</v>
       </c>
       <c r="H6" s="8">
         <v>45794.931250000001</v>
@@ -8029,28 +8051,31 @@
       <c r="J6" s="8">
         <v>45794.931250000001</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="8">
+        <v>45794.931250000001</v>
+      </c>
+      <c r="L6" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
         <v>347</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E7">
         <v>601170</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>348</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>349</v>
-      </c>
-      <c r="G7" s="8">
-        <v>45795.931250000001</v>
       </c>
       <c r="H7" s="8">
         <v>45795.931250000001</v>
@@ -8061,7 +8086,10 @@
       <c r="J7" s="8">
         <v>45795.931250000001</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="8">
+        <v>45795.931250000001</v>
+      </c>
+      <c r="L7" t="s">
         <v>351</v>
       </c>
     </row>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F1CC14-14A1-46F1-98F3-17FB8FA9C4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B5F9B4-6F50-4B05-A1D2-819E3BC0DE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="396">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1364,6 +1364,34 @@
   </si>
   <si>
     <t>SHEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中信城投期货</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210222198205135018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210222198205135017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62201234567908</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62201234567907</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M509</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7320,15 +7348,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6ABADF-5314-402D-971B-634CB3A368D4}">
-  <dimension ref="B2:K6"/>
+  <dimension ref="B2:L6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.375" customWidth="1"/>
+    <col min="7" max="12" width="36.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>239</v>
       </c>
@@ -7342,25 +7371,28 @@
         <v>271</v>
       </c>
       <c r="F2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G2" t="s">
         <v>312</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>355</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>356</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>316</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>317</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>0</v>
       </c>
@@ -7374,7 +7406,7 @@
         <v>371</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>372</v>
@@ -7391,8 +7423,11 @@
       <c r="K3" s="7" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L3" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>1</v>
       </c>
@@ -7405,26 +7440,29 @@
       <c r="E4" t="s">
         <v>309</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4">
+        <v>123456</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="L4" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2</v>
       </c>
@@ -7437,26 +7475,29 @@
       <c r="E5" t="s">
         <v>321</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5">
+        <v>123456</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="L5" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>3</v>
       </c>
@@ -7469,22 +7510,25 @@
       <c r="E6" t="s">
         <v>322</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6">
+        <v>123456</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="L6" t="s">
         <v>315</v>
       </c>
     </row>
@@ -7497,12 +7541,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{393D472E-32AC-4542-A27D-D437AC0EBDB2}">
-  <dimension ref="B2:J4"/>
+  <dimension ref="B2:J5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.75" bestFit="1" customWidth="1"/>
@@ -7570,7 +7615,7 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>286</v>
@@ -7582,10 +7627,10 @@
         <v>326</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>313</v>
+        <v>393</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>318</v>
@@ -7594,6 +7639,35 @@
         <v>318</v>
       </c>
       <c r="J4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J5" t="s">
         <v>327</v>
       </c>
     </row>
@@ -7874,13 +7948,14 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.375" customWidth="1"/>
-    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="10.375" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="13.625" customWidth="1"/>
     <col min="8" max="10" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="53.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.25" customWidth="1"/>
+    <col min="12" max="12" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.2">
@@ -7946,8 +8021,8 @@
       <c r="J3" s="8">
         <v>45792.931250000001</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>383</v>
+      <c r="K3" s="8">
+        <v>45792.931250000001</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>383</v>
@@ -8002,7 +8077,7 @@
         <v>337</v>
       </c>
       <c r="F5" t="s">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="G5" t="s">
         <v>338</v>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B5F9B4-6F50-4B05-A1D2-819E3BC0DE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E4C24F-A5CF-471D-9505-1F849B21DDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,12 @@
     <sheet name="T_clearinghouse" sheetId="8" r:id="rId8"/>
     <sheet name="t_security" sheetId="10" r:id="rId9"/>
     <sheet name="t_trader_security" sheetId="11" r:id="rId10"/>
-    <sheet name="t_settlement" sheetId="13" r:id="rId11"/>
-    <sheet name="t_transfer_journal" sheetId="14" r:id="rId12"/>
-    <sheet name="t_bank_account" sheetId="19" r:id="rId13"/>
-    <sheet name="t_future_account" sheetId="16" r:id="rId14"/>
-    <sheet name="t_stock_account" sheetId="17" r:id="rId15"/>
+    <sheet name="t_order" sheetId="20" r:id="rId11"/>
+    <sheet name="t_settlement" sheetId="13" r:id="rId12"/>
+    <sheet name="t_transfer_journal" sheetId="14" r:id="rId13"/>
+    <sheet name="t_bank_account" sheetId="19" r:id="rId14"/>
+    <sheet name="t_future_account" sheetId="16" r:id="rId15"/>
+    <sheet name="t_stock_account" sheetId="17" r:id="rId16"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="401">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1392,6 +1393,26 @@
   </si>
   <si>
     <t>M509</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LONG POSITION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QUANTITY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRADER_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1399,9 +1420,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.000"/>
     <numFmt numFmtId="177" formatCode="yyyy\-m\-d\ h:mm:ss"/>
+    <numFmt numFmtId="178" formatCode="yyyy/m/d\ h:mm:ss"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1448,7 +1470,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1458,6 +1480,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6481,6 +6504,79 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC51F45-DB58-4828-B9F8-B30FCB899E3C}">
+  <dimension ref="B105:I106"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B105" t="s">
+        <v>239</v>
+      </c>
+      <c r="C105" t="s">
+        <v>400</v>
+      </c>
+      <c r="D105" t="s">
+        <v>339</v>
+      </c>
+      <c r="E105" t="s">
+        <v>396</v>
+      </c>
+      <c r="F105" t="s">
+        <v>399</v>
+      </c>
+      <c r="G105" t="s">
+        <v>398</v>
+      </c>
+      <c r="H105" t="s">
+        <v>316</v>
+      </c>
+      <c r="I105" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106">
+        <v>10000.001</v>
+      </c>
+      <c r="G106">
+        <v>10</v>
+      </c>
+      <c r="H106" s="9">
+        <v>45791.59375</v>
+      </c>
+      <c r="I106" t="s">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED01824-373C-4B7A-A388-A735C9E31FD9}">
   <dimension ref="B2:G6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6596,7 +6692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F304A949-FFD7-49F1-B58D-74D342C4AF6C}">
   <dimension ref="B2:H4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6685,7 +6781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9305FC59-37FF-415A-A3B7-01239A431D79}">
   <dimension ref="B3:H5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6773,7 +6869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEE4E1E-4960-4128-9003-4ABF67067429}">
   <dimension ref="B2:H4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6859,7 +6955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883BD7DA-ECA5-459C-A285-7074F9420849}">
   <dimension ref="B3:G5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E4C24F-A5CF-471D-9505-1F849B21DDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C25329D-71A5-4CBF-89E1-015F0EB706C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
@@ -6558,7 +6558,7 @@
         <v>1</v>
       </c>
       <c r="F106">
-        <v>10000.001</v>
+        <v>1000</v>
       </c>
       <c r="G106">
         <v>10</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>347</v>
@@ -8231,7 +8231,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
         <v>347</v>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C25329D-71A5-4CBF-89E1-015F0EB706C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F77E2E-C57D-4949-ACBB-0E682B157E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="t_bank_account" sheetId="19" r:id="rId14"/>
     <sheet name="t_future_account" sheetId="16" r:id="rId15"/>
     <sheet name="t_stock_account" sheetId="17" r:id="rId16"/>
+    <sheet name="t_match_order" sheetId="21" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="404">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1413,6 +1414,18 @@
   </si>
   <si>
     <t>TRADER_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LONG_ORDER_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHORT_ORDER_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-----------------------------------------------------------------------------------</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7033,6 +7046,85 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A516BBE4-BD44-4075-A09D-D56A5035C2EE}">
+  <dimension ref="B2:J3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="92.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G2" t="s">
+        <v>398</v>
+      </c>
+      <c r="H2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="I3" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>403</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBFA0B0-09A3-4E87-9D3C-50BFACFA9A69}">
   <dimension ref="B2:F9"/>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F77E2E-C57D-4949-ACBB-0E682B157E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C8AFD8-CEA8-4687-B7F9-DA957D75C1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7055,7 +7055,7 @@
     <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="15.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="92.625" bestFit="1" customWidth="1"/>
@@ -7103,11 +7103,11 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3">
         <v>1000</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3">
         <v>45791.600694444445</v>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C8AFD8-CEA8-4687-B7F9-DA957D75C1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009B3269-9826-46E3-8CF6-2F787D81B20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="405">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1426,6 +1426,10 @@
   </si>
   <si>
     <t>-----------------------------------------------------------------------------------</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNMATCHED</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7048,7 +7052,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A516BBE4-BD44-4075-A09D-D56A5035C2EE}">
-  <dimension ref="B2:J3"/>
+  <dimension ref="B2:K3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
@@ -7057,11 +7061,12 @@
     <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="92.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="92.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>239</v>
       </c>
@@ -7081,16 +7086,19 @@
         <v>398</v>
       </c>
       <c r="H2" t="s">
+        <v>404</v>
+      </c>
+      <c r="I2" t="s">
         <v>316</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>317</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>1</v>
       </c>
@@ -7109,13 +7117,16 @@
       <c r="G3">
         <v>10</v>
       </c>
-      <c r="H3" s="3">
-        <v>45791.600694444445</v>
+      <c r="H3">
+        <v>10</v>
       </c>
       <c r="I3" s="3">
         <v>45791.600694444445</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="3">
+        <v>45791.600694444445</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>403</v>
       </c>
     </row>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009B3269-9826-46E3-8CF6-2F787D81B20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BF35EE-AEB0-4D29-A0E5-7DCA0D77180F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
@@ -6522,7 +6522,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC51F45-DB58-4828-B9F8-B30FCB899E3C}">
-  <dimension ref="B105:I106"/>
+  <dimension ref="B2:J3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
@@ -6531,59 +6531,66 @@
     <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B105" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
         <v>239</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C2" t="s">
         <v>400</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D2" t="s">
         <v>339</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E2" t="s">
         <v>396</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F2" t="s">
         <v>399</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G2" t="s">
         <v>398</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H2" t="s">
+        <v>404</v>
+      </c>
+      <c r="I2" t="s">
         <v>316</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B106">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3">
         <v>0</v>
       </c>
-      <c r="C106">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D106">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E106">
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="F106">
+      <c r="F3">
         <v>1000</v>
       </c>
-      <c r="G106">
+      <c r="G3">
         <v>10</v>
       </c>
-      <c r="H106" s="9">
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3" s="9">
         <v>45791.59375</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J3" t="s">
         <v>397</v>
       </c>
     </row>
@@ -7052,7 +7059,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A516BBE4-BD44-4075-A09D-D56A5035C2EE}">
-  <dimension ref="B2:K3"/>
+  <dimension ref="B2:J3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
@@ -7061,12 +7068,11 @@
     <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="92.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="92.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>239</v>
       </c>
@@ -7086,19 +7092,16 @@
         <v>398</v>
       </c>
       <c r="H2" t="s">
-        <v>404</v>
+        <v>316</v>
       </c>
       <c r="I2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J2" t="s">
-        <v>317</v>
-      </c>
-      <c r="K2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>1</v>
       </c>
@@ -7117,16 +7120,13 @@
       <c r="G3">
         <v>10</v>
       </c>
-      <c r="H3">
-        <v>10</v>
+      <c r="H3" s="3">
+        <v>45791.600694444445</v>
       </c>
       <c r="I3" s="3">
         <v>45791.600694444445</v>
       </c>
-      <c r="J3" s="3">
-        <v>45791.600694444445</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>403</v>
       </c>
     </row>

--- a/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/myfuture/api/model/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\myfuture\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BF35EE-AEB0-4D29-A0E5-7DCA0D77180F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FCE9F1-3A1B-4B48-B2FC-AE5CA183AB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="406">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -1430,6 +1430,10 @@
   </si>
   <si>
     <t>UNMATCHED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REVISION</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6522,21 +6526,23 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC51F45-DB58-4828-B9F8-B30FCB899E3C}">
-  <dimension ref="B2:J3"/>
+  <dimension ref="B2:L3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>239</v>
       </c>
@@ -6559,13 +6565,19 @@
         <v>404</v>
       </c>
       <c r="I2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K2" t="s">
         <v>316</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>0</v>
       </c>
@@ -6587,10 +6599,16 @@
       <c r="H3">
         <v>10</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="9">
         <v>45791.59375</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" s="9">
+        <v>45791.59375</v>
+      </c>
+      <c r="L3" t="s">
         <v>397</v>
       </c>
     </row>
